--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1775548926" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1775548926" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1775548926" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1775548926"/>
+      <pm:revision xmlns:pm="smNativeData" day="1775628981" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1775628981" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1775628981" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1775628981"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775548926" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775628981" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775548926" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775628981" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775548926"/>
+          <pm:border xmlns:pm="smNativeData" id="1775628981"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775548926"/>
+          <pm:border xmlns:pm="smNativeData" id="1775628981"/>
         </ext>
       </extLst>
     </border>
@@ -153,7 +153,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1775548926" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1775628981" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -450,7 +450,7 @@
         <v>0.666666666666666519</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.711111111111111249</v>
+        <v>0.71111111111111116</v>
       </c>
       <c r="E3" s="3">
         <f>D3-C3</f>
@@ -604,12 +604,32 @@
         <v>0.0479166666666669983</v>
       </c>
     </row>
-    <row r="15" spans="3:3">
-      <c r="C15" s="4" t="n">
-        <v>0.458333333333333304</v>
-      </c>
-    </row>
-    <row r="16" spans="6:6">
+    <row r="15" spans="3:5">
+      <c r="C15" s="1" t="n">
+        <v>0.458333333333333215</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0.463888888888888928</v>
+      </c>
+      <c r="E15" s="3">
+        <f>D15-C15</f>
+        <v>0.00555555555555603497</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0.359722222222222232</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.386111111111111107</v>
+      </c>
+      <c r="E16" s="3">
+        <f>D16-C16</f>
+        <v>0.0263888888888890172</v>
+      </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="6:7">
@@ -627,7 +647,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1775548926" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1775628981" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -636,16 +656,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1775548926" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1775548926" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775548926" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775548926" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1775628981" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1775628981" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775628981" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775628981" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775548926" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775628981" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1775628981" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1775628981" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1775628981" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1775628981"/>
+      <pm:revision xmlns:pm="smNativeData" day="1775799973" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1775799973" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1775799973" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1775799973"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775628981" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775799973" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775628981" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775799973" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775628981"/>
+          <pm:border xmlns:pm="smNativeData" id="1775799973"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775628981"/>
+          <pm:border xmlns:pm="smNativeData" id="1775799973"/>
         </ext>
       </extLst>
     </border>
@@ -153,7 +153,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1775628981" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1775799973" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -450,7 +450,7 @@
         <v>0.666666666666666519</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.71111111111111116</v>
+        <v>0.711111111111111249</v>
       </c>
       <c r="E3" s="3">
         <f>D3-C3</f>
@@ -620,10 +620,10 @@
       <c r="B16" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="1" t="n">
         <v>0.359722222222222232</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="1" t="n">
         <v>0.386111111111111107</v>
       </c>
       <c r="E16" s="3">
@@ -632,7 +632,20 @@
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:7">
+    <row r="17" spans="2:7">
+      <c r="B17" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0.666666666666666607</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.729166666666666607</v>
+      </c>
+      <c r="E17" s="3">
+        <f>D17-C17</f>
+        <v>0.0625</v>
+      </c>
       <c r="F17"/>
       <c r="G17"/>
     </row>
@@ -647,7 +660,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1775628981" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1775799973" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -656,16 +669,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1775628981" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1775628981" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775628981" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775628981" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1775799973" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1775799973" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775799973" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775799973" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775628981" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775799973" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1775799973" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1775799973" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1775799973" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1775799973"/>
+      <pm:revision xmlns:pm="smNativeData" day="1775804802" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1775804802" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1775804802" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1775804802"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775799973" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775804802" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775799973" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775804802" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775799973"/>
+          <pm:border xmlns:pm="smNativeData" id="1775804802"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775799973"/>
+          <pm:border xmlns:pm="smNativeData" id="1775804802"/>
         </ext>
       </extLst>
     </border>
@@ -140,11 +140,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -153,7 +155,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1775799973" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1775804802" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -649,18 +651,34 @@
       <c r="F17"/>
       <c r="G17"/>
     </row>
-    <row r="18" spans="6:7">
+    <row r="18" spans="2:7">
+      <c r="B18" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.406944444444444464</v>
+      </c>
+      <c r="E18" s="3">
+        <f>D18-C18</f>
+        <v>0.0388888888888879727</v>
+      </c>
       <c r="F18"/>
       <c r="G18"/>
     </row>
-    <row r="19" spans="7:7">
+    <row r="19" spans="3:7">
+      <c r="C19" s="6" t="n">
+        <v>0.422222222222222232</v>
+      </c>
       <c r="G19"/>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1775799973" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1775804802" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -669,16 +687,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1775799973" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1775799973" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775799973" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775799973" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1775804802" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1775804802" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775804802" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775804802" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775799973" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775804802" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1775804802" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1775804802" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1775804802" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1775804802"/>
+      <pm:revision xmlns:pm="smNativeData" day="1775815889" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1775815889" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1775815889" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1775815889"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775804802" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1775815889" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775804802" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1775815889" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775804802"/>
+          <pm:border xmlns:pm="smNativeData" id="1775815889"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775804802"/>
+          <pm:border xmlns:pm="smNativeData" id="1775815889"/>
         </ext>
       </extLst>
     </border>
@@ -140,13 +140,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -155,7 +153,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1775804802" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1775815889" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -419,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A2:G19"/>
+  <dimension ref="A2:G20"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="30.000000" customWidth="1"/>
@@ -452,7 +450,7 @@
         <v>0.666666666666666519</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.711111111111111249</v>
+        <v>0.71111111111111116</v>
       </c>
       <c r="E3" s="3">
         <f>D3-C3</f>
@@ -638,11 +636,11 @@
       <c r="B17" s="2" t="n">
         <v>46121</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>0.666666666666666607</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0.729166666666666607</v>
+      <c r="C17" s="1" t="n">
+        <v>0.666666666666666519</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0.729166666666666519</v>
       </c>
       <c r="E17" s="3">
         <f>D17-C17</f>
@@ -655,30 +653,42 @@
       <c r="B18" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="1" t="n">
         <v>0.36805555555555558</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="1" t="n">
         <v>0.406944444444444464</v>
       </c>
       <c r="E18" s="3">
         <f>D18-C18</f>
-        <v>0.0388888888888879727</v>
+        <v>0.0388888888888889728</v>
       </c>
       <c r="F18"/>
       <c r="G18"/>
     </row>
     <row r="19" spans="3:7">
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="1" t="n">
         <v>0.422222222222222232</v>
       </c>
+      <c r="D19" s="1" t="n">
+        <v>0.464583333333333393</v>
+      </c>
+      <c r="E19" s="3">
+        <f>D19-C19</f>
+        <v>0.0423611111111110183</v>
+      </c>
       <c r="G19"/>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="4" t="n">
+        <v>0.541666666666666607</v>
+      </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1775804802" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1775815889" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -687,16 +697,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1775804802" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1775804802" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775804802" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775804802" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1775815889" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1775815889" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775815889" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1775815889" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775804802" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775815889" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1775815889" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1775815889" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1775815889" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1775815889"/>
+      <pm:revision xmlns:pm="smNativeData" day="1776058515" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1776058515" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1776058515" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1776058515"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1775815889" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776058515" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1775815889" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1776058515" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775815889"/>
+          <pm:border xmlns:pm="smNativeData" id="1776058515"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1775815889"/>
+          <pm:border xmlns:pm="smNativeData" id="1776058515"/>
         </ext>
       </extLst>
     </border>
@@ -140,11 +140,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -153,7 +154,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1775815889" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1776058515" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -417,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A2:G20"/>
+  <dimension ref="A2:G21"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="30.000000" customWidth="1"/>
@@ -450,7 +451,7 @@
         <v>0.666666666666666519</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.71111111111111116</v>
+        <v>0.711111111111111249</v>
       </c>
       <c r="E3" s="3">
         <f>D3-C3</f>
@@ -679,16 +680,31 @@
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="4" t="n">
-        <v>0.541666666666666607</v>
+    <row r="20" spans="3:5">
+      <c r="C20" s="1" t="n">
+        <v>0.541666666666666519</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E20" s="3">
+        <f>D20-C20</f>
+        <v>0.0833333333333330373</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.356944444444444464</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1775815889" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776058515" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -697,16 +713,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1775815889" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1775815889" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775815889" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1775815889" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1776058515" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776058515" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776058515" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776058515" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1775815889" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776058515" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1776058515" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1776058515" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1776058515" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1776058515"/>
+      <pm:revision xmlns:pm="smNativeData" day="1776061048" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1776061048" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1776061048" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1776061048"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1776058515" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776061048" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1776058515" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1776061048" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1776058515"/>
+          <pm:border xmlns:pm="smNativeData" id="1776061048"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1776058515"/>
+          <pm:border xmlns:pm="smNativeData" id="1776061048"/>
         </ext>
       </extLst>
     </border>
@@ -140,11 +140,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -154,7 +155,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1776058515" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1776061048" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -692,19 +693,26 @@
         <v>0.0833333333333330373</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
+    <row r="21" spans="2:5">
       <c r="B21" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>0.356944444444444464</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.386805555555555571</v>
+      </c>
+      <c r="E21" s="3">
+        <f>D21-C21</f>
+        <v>0.0298611111111110041</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1776058515" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776061048" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -713,16 +721,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1776058515" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1776058515" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1776058515" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1776058515" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1776061048" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776061048" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776061048" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776061048" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776058515" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776061048" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1776061048" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1776061048" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1776061048" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1776061048"/>
+      <pm:revision xmlns:pm="smNativeData" day="1776148620" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1776148620" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1776148620" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1776148620"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1776061048" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776148620" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1776061048" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1776148620" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1776061048"/>
+          <pm:border xmlns:pm="smNativeData" id="1776148620"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1776061048"/>
+          <pm:border xmlns:pm="smNativeData" id="1776148620"/>
         </ext>
       </extLst>
     </border>
@@ -140,13 +140,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -155,7 +153,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1776061048" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1776148620" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -419,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A2:G21"/>
+  <dimension ref="A2:G22"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="30.000000" customWidth="1"/>
@@ -452,7 +450,7 @@
         <v>0.666666666666666519</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.711111111111111249</v>
+        <v>0.71111111111111116</v>
       </c>
       <c r="E3" s="3">
         <f>D3-C3</f>
@@ -685,7 +683,7 @@
       <c r="C20" s="1" t="n">
         <v>0.541666666666666519</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="1" t="n">
         <v>0.625</v>
       </c>
       <c r="E20" s="3">
@@ -697,22 +695,30 @@
       <c r="B21" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="1" t="n">
         <v>0.356944444444444464</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="1" t="n">
         <v>0.386805555555555571</v>
       </c>
       <c r="E21" s="3">
         <f>D21-C21</f>
         <v>0.0298611111111110041</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1776061048" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776148620" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -721,16 +727,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1776061048" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1776061048" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1776061048" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1776061048" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1776148620" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776148620" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776148620" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776148620" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776061048" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776148620" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/local/время-выполнения.xlsx
+++ b/local/время-выполнения.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1776148620" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1776148620" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1776148620" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1776148620"/>
+      <pm:revision xmlns:pm="smNativeData" day="1776160396" val="1068" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1776160396" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1776160396" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1776160396"/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +69,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1776148620" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1776160396" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -91,7 +91,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1776148620" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1776160396" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -113,7 +113,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1776148620"/>
+          <pm:border xmlns:pm="smNativeData" id="1776160396"/>
         </ext>
       </extLst>
     </border>
@@ -132,7 +132,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1776148620"/>
+          <pm:border xmlns:pm="smNativeData" id="1776160396"/>
         </ext>
       </extLst>
     </border>
@@ -153,7 +153,7 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1776148620" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1776160396" count="1">
         <pm:charStyle name="Обычный" fontId="0"/>
       </pm:charStyles>
     </ext>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A2:G22"/>
+  <dimension ref="A2:G23"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="30.000000" customWidth="1"/>
@@ -450,7 +450,7 @@
         <v>0.666666666666666519</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.71111111111111116</v>
+        <v>0.711111111111111249</v>
       </c>
       <c r="E3" s="3">
         <f>D3-C3</f>
@@ -706,19 +706,31 @@
         <v>0.0298611111111110041</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
+    <row r="22" spans="2:5">
       <c r="B22" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="1" t="n">
         <v>0.4</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0.449305555555555536</v>
+      </c>
+      <c r="E22" s="3">
+        <f>D22-C22</f>
+        <v>0.0493055555555559888</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="4" t="n">
+        <v>0.536111111111111072</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1776148620" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1776160396" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -727,16 +739,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1776148620" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1776148620" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1776148620" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1776148620" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1776160396" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1776160396" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776160396" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1776160396" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776148620" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1776160396" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
